--- a/backend/config/strauss-data.xlsx
+++ b/backend/config/strauss-data.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>חישוב חודשי (לא מצטבר), לוחות 2025: מדרגות מס, 242 ₪ לנקודת זיכוי, ביטוח לאומי ובריאות בשתי מדרגות, זיכוי 35% על פנסיית העובד. שווי השימוש מתווסף לבסיס המס ולביטוח הלאומי. 6 עובדים לדוגמה עם נטו ייחוס להיום ולחלופה - גיליונות ׳עובדים לדוגמה׳ ו׳חישובים׳.</t>
+          <t>חישוב חודשי (לא מצטבר), לוחות 2025: מדרגות מס, 242 ₪ לנקודת זיכוי, ביטוח לאומי ובריאות בשתי מדרגות. זיכוי 35% על פנסיית העובד עד 7% מהכנסה מזכה של 9,500 ₪ (עד 232.75 ₪, לכן זהה בכל הדוגמאות). פנסיה וקה״ש מחושבות על כל הברוטו כולל עמלות ובונוס. שווי השימוש מתווסף לבסיס המס ולביטוח הלאומי; השתתפות ברכב יורדת מהנטו בלבד. גילום החזר החשמל ללא עיגול, עיגול לשקל רק בתצוגה. 6 עובדים לדוגמה עם נטו ייחוס - גיליונות ׳עובדים לדוגמה׳ ו׳חישובים׳.</t>
         </is>
       </c>
     </row>
